--- a/demo/samples/bearings/02-stock-statement.xlsx
+++ b/demo/samples/bearings/02-stock-statement.xlsx
@@ -449,7 +449,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stock as on 16-09-2026</t>
+          <t>Stock as on 21-09-2026</t>
         </is>
       </c>
     </row>
